--- a/Versão5/CRON/Ontologia_CRONO.xlsx
+++ b/Versão5/CRON/Ontologia_CRONO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CRON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB59D993-662A-439A-A32F-E106D77EBFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100D8441-2E28-463F-8561-B598E1C331CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2829" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="484">
   <si>
     <t>Key</t>
   </si>
@@ -1628,9 +1628,6 @@
     <t>Alv.Térreo</t>
   </si>
   <si>
-    <t>"Evento real acontecido em projeto ou obra."</t>
-  </si>
-  <si>
     <t>Liga.Bomba</t>
   </si>
   <si>
@@ -2614,9 +2611,6 @@
     <t>classe.ifc</t>
   </si>
   <si>
-    <t>"-"</t>
-  </si>
-  <si>
     <t>Ano.2026</t>
   </si>
   <si>
@@ -2675,6 +2669,51 @@
   </si>
   <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>"Primeiro quatrimestre do ano."</t>
+  </si>
+  <si>
+    <t>"Segundo quatrimestre do ano."</t>
+  </si>
+  <si>
+    <t>"Terceiro quatrimestre do ano."</t>
+  </si>
+  <si>
+    <t>"Um evento real acontecido referente às alvenarias em projeto ou obra qualquer."</t>
+  </si>
+  <si>
+    <t>tema</t>
+  </si>
+  <si>
+    <t>"Planejamento"</t>
+  </si>
+  <si>
+    <t>subtema</t>
+  </si>
+  <si>
+    <t>"Meses do ano"</t>
+  </si>
+  <si>
+    <t>"Dias da semana"</t>
+  </si>
+  <si>
+    <t>"Alvenarias"</t>
+  </si>
+  <si>
+    <t>"Cronogramas"</t>
+  </si>
+  <si>
+    <t>"Etapas de Projeto"</t>
+  </si>
+  <si>
+    <t>"Testes realizados"</t>
+  </si>
+  <si>
+    <t>"Calendário"</t>
+  </si>
+  <si>
+    <t>"[ - ]"</t>
   </si>
 </sst>
 </file>
@@ -3264,15 +3303,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3371,6 +3402,22 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3408,22 +3455,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3780,294 +3811,294 @@
   <sheetData>
     <row r="1" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C1" s="57" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B5" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" s="14" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C8" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>158</v>
-      </c>
       <c r="C9" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46139.489624421294</v>
+        <v>46143.59318935185</v>
       </c>
       <c r="C18" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="61" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="B19" s="60" t="s">
         <v>444</v>
       </c>
-      <c r="B19" s="60" t="s">
-        <v>445</v>
-      </c>
       <c r="C19" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="61" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B20" s="60" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones integradas al español e inglés - Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="61" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B21" s="60" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","en")</f>
         <v>Built-in Spanish and English Translations - Translations must be constantly reviewed</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="58" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C25" s="58" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" spans="1:3" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B26" s="18" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize Concepts of Time Elements</v>
       </c>
       <c r="C26" s="58" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -4105,22 +4136,22 @@
   <sheetData>
     <row r="1" spans="1:27" ht="40.299999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="D1" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="E1" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F1" s="23" t="s">
         <v>180</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>181</v>
       </c>
       <c r="G1" s="24" t="s">
         <v>39</v>
@@ -4150,40 +4181,40 @@
         <v>44</v>
       </c>
       <c r="P1" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q1" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="R1" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="R1" s="26" t="s">
+      <c r="S1" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="T1" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="U1" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="V1" s="25" t="s">
         <v>174</v>
-      </c>
-      <c r="T1" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="U1" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="V1" s="25" t="s">
-        <v>175</v>
       </c>
       <c r="W1" s="72" t="s">
         <v>0</v>
       </c>
       <c r="X1" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="Y1" s="25" t="s">
         <v>434</v>
       </c>
-      <c r="Y1" s="25" t="s">
+      <c r="Z1" s="25" t="s">
         <v>435</v>
       </c>
-      <c r="Z1" s="25" t="s">
+      <c r="AA1" s="55" t="s">
         <v>436</v>
-      </c>
-      <c r="AA1" s="55" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -4191,19 +4222,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C2" s="65" t="s">
+        <v>453</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>454</v>
+      </c>
+      <c r="E2" s="64" t="s">
         <v>455</v>
       </c>
-      <c r="D2" s="64" t="s">
-        <v>456</v>
-      </c>
-      <c r="E2" s="64" t="s">
-        <v>457</v>
-      </c>
       <c r="F2" s="65" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G2" s="66" t="s">
         <v>1</v>
@@ -4237,10 +4268,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="56" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="Q2" s="56" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R2" s="68" t="s">
         <v>1</v>
@@ -4258,7 +4289,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W2" s="73" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.CRON",".",A2)</f>
@@ -4283,19 +4314,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="64" t="s">
+        <v>459</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>453</v>
+      </c>
+      <c r="D3" s="64" t="s">
+        <v>454</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>458</v>
+      </c>
+      <c r="F3" s="65" t="s">
         <v>461</v>
-      </c>
-      <c r="C3" s="65" t="s">
-        <v>455</v>
-      </c>
-      <c r="D3" s="64" t="s">
-        <v>456</v>
-      </c>
-      <c r="E3" s="64" t="s">
-        <v>460</v>
-      </c>
-      <c r="F3" s="65" t="s">
-        <v>463</v>
       </c>
       <c r="G3" s="66" t="s">
         <v>1</v>
@@ -4329,10 +4360,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="56" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="Q3" s="56" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R3" s="68" t="s">
         <v>1</v>
@@ -4350,7 +4381,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W3" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4375,19 +4406,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C4" s="65" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E4" s="64" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F4" s="65" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G4" s="66" t="s">
         <v>1</v>
@@ -4421,10 +4452,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="56" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="Q4" s="56" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R4" s="68" t="s">
         <v>1</v>
@@ -4442,7 +4473,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W4" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4467,19 +4498,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D5" s="64" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E5" s="64" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F5" s="65" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G5" s="66" t="s">
         <v>1</v>
@@ -4513,10 +4544,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="56" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="Q5" s="56" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R5" s="68" t="s">
         <v>1</v>
@@ -4534,7 +4565,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W5" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4559,19 +4590,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E6" s="64" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F6" s="65" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G6" s="66" t="s">
         <v>1</v>
@@ -4605,10 +4636,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="56" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="Q6" s="56" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="R6" s="68" t="s">
         <v>1</v>
@@ -4626,7 +4657,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W6" s="73" t="str">
         <f t="shared" si="3"/>
@@ -4651,10 +4682,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D7" s="29" t="s">
         <v>59</v>
@@ -4697,10 +4728,10 @@
         <v>Era</v>
       </c>
       <c r="P7" s="70" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Q7" s="70" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R7" s="68" t="s">
         <v>1</v>
@@ -4718,7 +4749,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V7" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W7" s="73" t="str">
         <f t="shared" ref="W7:W48" si="8">CONCATENATE("Key.CRON",".",A7)</f>
@@ -4743,10 +4774,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C8" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D8" s="29" t="s">
         <v>59</v>
@@ -4789,10 +4820,10 @@
         <v>Época</v>
       </c>
       <c r="P8" s="70" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Q8" s="70" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R8" s="68" t="s">
         <v>1</v>
@@ -4810,7 +4841,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V8" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W8" s="73" t="str">
         <f t="shared" si="8"/>
@@ -4835,10 +4866,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D9" s="29" t="s">
         <v>59</v>
@@ -4847,7 +4878,7 @@
         <v>63</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G9" s="66" t="s">
         <v>1</v>
@@ -4881,10 +4912,10 @@
         <v>Século</v>
       </c>
       <c r="P9" s="70" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q9" s="70" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R9" s="68" t="s">
         <v>1</v>
@@ -4902,7 +4933,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V9" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W9" s="73" t="str">
         <f t="shared" si="8"/>
@@ -4927,10 +4958,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C10" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D10" s="29" t="s">
         <v>59</v>
@@ -4939,7 +4970,7 @@
         <v>63</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G10" s="66" t="s">
         <v>1</v>
@@ -4973,10 +5004,10 @@
         <v>Quinquagenário</v>
       </c>
       <c r="P10" s="70" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Q10" s="70" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R10" s="68" t="s">
         <v>1</v>
@@ -4994,7 +5025,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V10" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W10" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5019,10 +5050,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>59</v>
@@ -5031,7 +5062,7 @@
         <v>63</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G11" s="66" t="s">
         <v>1</v>
@@ -5065,10 +5096,10 @@
         <v>Década</v>
       </c>
       <c r="P11" s="70" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q11" s="70" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R11" s="68" t="s">
         <v>1</v>
@@ -5086,7 +5117,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V11" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W11" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5111,10 +5142,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C12" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D12" s="29" t="s">
         <v>59</v>
@@ -5123,7 +5154,7 @@
         <v>63</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G12" s="66" t="s">
         <v>1</v>
@@ -5157,10 +5188,10 @@
         <v>Quinquênio</v>
       </c>
       <c r="P12" s="70" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q12" s="70" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R12" s="68" t="s">
         <v>1</v>
@@ -5178,7 +5209,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V12" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W12" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5203,10 +5234,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D13" s="29" t="s">
         <v>59</v>
@@ -5215,7 +5246,7 @@
         <v>63</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G13" s="66" t="s">
         <v>1</v>
@@ -5249,10 +5280,10 @@
         <v>Lustro</v>
       </c>
       <c r="P13" s="70" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q13" s="70" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R13" s="68" t="s">
         <v>1</v>
@@ -5270,7 +5301,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V13" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W13" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5295,10 +5326,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C14" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D14" s="29" t="s">
         <v>59</v>
@@ -5307,7 +5338,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G14" s="66" t="s">
         <v>1</v>
@@ -5341,10 +5372,10 @@
         <v>Biênio</v>
       </c>
       <c r="P14" s="70" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Q14" s="70" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R14" s="68" t="s">
         <v>1</v>
@@ -5362,7 +5393,7 @@
         <v>Macroevento</v>
       </c>
       <c r="V14" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W14" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5387,10 +5418,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D15" s="29" t="s">
         <v>59</v>
@@ -5433,10 +5464,10 @@
         <v>Ano</v>
       </c>
       <c r="P15" s="70" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Q15" s="70" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R15" s="68" t="s">
         <v>1</v>
@@ -5454,7 +5485,7 @@
         <v>Calendário</v>
       </c>
       <c r="V15" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W15" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5479,10 +5510,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D16" s="29" t="s">
         <v>59</v>
@@ -5491,7 +5522,7 @@
         <v>61</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G16" s="66" t="s">
         <v>1</v>
@@ -5525,10 +5556,10 @@
         <v>Semestre</v>
       </c>
       <c r="P16" s="70" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q16" s="70" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R16" s="68" t="s">
         <v>1</v>
@@ -5546,7 +5577,7 @@
         <v>Calendário</v>
       </c>
       <c r="V16" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W16" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5571,10 +5602,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D17" s="29" t="s">
         <v>59</v>
@@ -5583,7 +5614,7 @@
         <v>61</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G17" s="66" t="s">
         <v>1</v>
@@ -5617,10 +5648,10 @@
         <v>Quatrimestre</v>
       </c>
       <c r="P17" s="70" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Q17" s="70" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R17" s="68" t="s">
         <v>1</v>
@@ -5638,7 +5669,7 @@
         <v>Calendário</v>
       </c>
       <c r="V17" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W17" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5663,10 +5694,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D18" s="29" t="s">
         <v>59</v>
@@ -5675,7 +5706,7 @@
         <v>61</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G18" s="66" t="s">
         <v>1</v>
@@ -5709,10 +5740,10 @@
         <v>Trimestre</v>
       </c>
       <c r="P18" s="70" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q18" s="70" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R18" s="68" t="s">
         <v>1</v>
@@ -5730,7 +5761,7 @@
         <v>Calendário</v>
       </c>
       <c r="V18" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W18" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5755,10 +5786,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D19" s="29" t="s">
         <v>59</v>
@@ -5801,10 +5832,10 @@
         <v>Mês</v>
       </c>
       <c r="P19" s="70" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q19" s="70" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R19" s="68" t="s">
         <v>1</v>
@@ -5822,7 +5853,7 @@
         <v>Calendário</v>
       </c>
       <c r="V19" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W19" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5847,10 +5878,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C20" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D20" s="29" t="s">
         <v>59</v>
@@ -5893,10 +5924,10 @@
         <v>Semana</v>
       </c>
       <c r="P20" s="70" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q20" s="70" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R20" s="68" t="s">
         <v>1</v>
@@ -5914,7 +5945,7 @@
         <v>Calendário</v>
       </c>
       <c r="V20" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W20" s="73" t="str">
         <f t="shared" si="8"/>
@@ -5939,10 +5970,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C21" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D21" s="29" t="s">
         <v>59</v>
@@ -5985,10 +6016,10 @@
         <v>Dia</v>
       </c>
       <c r="P21" s="70" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q21" s="70" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="R21" s="68" t="s">
         <v>1</v>
@@ -6006,7 +6037,7 @@
         <v>Calendário</v>
       </c>
       <c r="V21" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W21" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6031,10 +6062,10 @@
         <v>22</v>
       </c>
       <c r="B22" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C22" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>59</v>
@@ -6043,7 +6074,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G22" s="66" t="s">
         <v>1</v>
@@ -6077,10 +6108,10 @@
         <v>Jornada</v>
       </c>
       <c r="P22" s="70" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q22" s="70" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="R22" s="68" t="s">
         <v>1</v>
@@ -6098,7 +6129,7 @@
         <v>Calendário</v>
       </c>
       <c r="V22" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W22" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6123,10 +6154,10 @@
         <v>23</v>
       </c>
       <c r="B23" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>59</v>
@@ -6169,10 +6200,10 @@
         <v>Hora</v>
       </c>
       <c r="P23" s="70" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q23" s="70" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R23" s="68" t="s">
         <v>1</v>
@@ -6190,7 +6221,7 @@
         <v>Horário</v>
       </c>
       <c r="V23" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W23" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6215,10 +6246,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D24" s="29" t="s">
         <v>59</v>
@@ -6261,10 +6292,10 @@
         <v>Minuto</v>
       </c>
       <c r="P24" s="70" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q24" s="70" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R24" s="68" t="s">
         <v>1</v>
@@ -6282,7 +6313,7 @@
         <v>Horário</v>
       </c>
       <c r="V24" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W24" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6307,10 +6338,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C25" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>59</v>
@@ -6353,10 +6384,10 @@
         <v>Segundo</v>
       </c>
       <c r="P25" s="70" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q25" s="70" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R25" s="68" t="s">
         <v>1</v>
@@ -6374,7 +6405,7 @@
         <v>Horário</v>
       </c>
       <c r="V25" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W25" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6399,10 +6430,10 @@
         <v>26</v>
       </c>
       <c r="B26" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C26" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D26" s="29" t="s">
         <v>59</v>
@@ -6445,7 +6476,7 @@
         <v>Milisegundo</v>
       </c>
       <c r="P26" s="70" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q26" s="70" t="s">
         <v>58</v>
@@ -6466,7 +6497,7 @@
         <v>Horário</v>
       </c>
       <c r="V26" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W26" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6491,10 +6522,10 @@
         <v>27</v>
       </c>
       <c r="B27" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C27" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>59</v>
@@ -6537,10 +6568,10 @@
         <v>Pulso</v>
       </c>
       <c r="P27" s="70" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q27" s="70" t="s">
         <v>369</v>
-      </c>
-      <c r="Q27" s="70" t="s">
-        <v>370</v>
       </c>
       <c r="R27" s="68" t="s">
         <v>1</v>
@@ -6558,7 +6589,7 @@
         <v>Microevento</v>
       </c>
       <c r="V27" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W27" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6583,10 +6614,10 @@
         <v>28</v>
       </c>
       <c r="B28" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>59</v>
@@ -6629,10 +6660,10 @@
         <v>Tick</v>
       </c>
       <c r="P28" s="70" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q28" s="70" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R28" s="68" t="s">
         <v>1</v>
@@ -6650,7 +6681,7 @@
         <v>Microevento</v>
       </c>
       <c r="V28" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W28" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6675,19 +6706,19 @@
         <v>29</v>
       </c>
       <c r="B29" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D29" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G29" s="66" t="s">
         <v>1</v>
@@ -6721,10 +6752,10 @@
         <v>Inicial</v>
       </c>
       <c r="P29" s="70" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q29" s="70" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="R29" s="68" t="s">
         <v>1</v>
@@ -6742,7 +6773,7 @@
         <v>Cronómetro</v>
       </c>
       <c r="V29" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W29" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6767,19 +6798,19 @@
         <v>30</v>
       </c>
       <c r="B30" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D30" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E30" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="F30" s="28" t="s">
         <v>375</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>376</v>
       </c>
       <c r="G30" s="66" t="s">
         <v>1</v>
@@ -6813,10 +6844,10 @@
         <v>Parcial</v>
       </c>
       <c r="P30" s="70" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Q30" s="70" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="R30" s="68" t="s">
         <v>1</v>
@@ -6834,7 +6865,7 @@
         <v>Cronómetro</v>
       </c>
       <c r="V30" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W30" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6859,19 +6890,19 @@
         <v>31</v>
       </c>
       <c r="B31" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C31" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D31" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G31" s="66" t="s">
         <v>1</v>
@@ -6905,10 +6936,10 @@
         <v>Final</v>
       </c>
       <c r="P31" s="70" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q31" s="70" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R31" s="68" t="s">
         <v>1</v>
@@ -6926,7 +6957,7 @@
         <v>Cronómetro</v>
       </c>
       <c r="V31" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W31" s="73" t="str">
         <f t="shared" si="8"/>
@@ -6951,10 +6982,10 @@
         <v>32</v>
       </c>
       <c r="B32" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D32" s="29" t="s">
         <v>59</v>
@@ -6997,10 +7028,10 @@
         <v>DeltaT</v>
       </c>
       <c r="P32" s="70" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q32" s="70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R32" s="68" t="s">
         <v>1</v>
@@ -7018,7 +7049,7 @@
         <v>Duração</v>
       </c>
       <c r="V32" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W32" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7043,16 +7074,16 @@
         <v>33</v>
       </c>
       <c r="B33" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C33" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D33" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F33" s="28" t="s">
         <v>68</v>
@@ -7089,10 +7120,10 @@
         <v>Ideação</v>
       </c>
       <c r="P33" s="70" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q33" s="70" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R33" s="68" t="s">
         <v>1</v>
@@ -7110,7 +7141,7 @@
         <v>Etapa</v>
       </c>
       <c r="V33" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W33" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7135,16 +7166,16 @@
         <v>34</v>
       </c>
       <c r="B34" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C34" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C34" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D34" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F34" s="28" t="s">
         <v>73</v>
@@ -7181,10 +7212,10 @@
         <v>Projetual</v>
       </c>
       <c r="P34" s="70" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q34" s="70" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R34" s="68" t="s">
         <v>1</v>
@@ -7202,7 +7233,7 @@
         <v>Etapa</v>
       </c>
       <c r="V34" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W34" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7227,16 +7258,16 @@
         <v>35</v>
       </c>
       <c r="B35" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C35" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D35" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F35" s="29" t="s">
         <v>69</v>
@@ -7273,10 +7304,10 @@
         <v>Simulação</v>
       </c>
       <c r="P35" s="70" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q35" s="70" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R35" s="68" t="s">
         <v>1</v>
@@ -7294,7 +7325,7 @@
         <v>Etapa</v>
       </c>
       <c r="V35" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W35" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7319,16 +7350,16 @@
         <v>36</v>
       </c>
       <c r="B36" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C36" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C36" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D36" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F36" s="29" t="s">
         <v>70</v>
@@ -7365,10 +7396,10 @@
         <v>Planejamento</v>
       </c>
       <c r="P36" s="70" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q36" s="70" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R36" s="68" t="s">
         <v>1</v>
@@ -7386,7 +7417,7 @@
         <v>Etapa</v>
       </c>
       <c r="V36" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W36" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7411,16 +7442,16 @@
         <v>37</v>
       </c>
       <c r="B37" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C37" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C37" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D37" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F37" s="29" t="s">
         <v>72</v>
@@ -7457,10 +7488,10 @@
         <v>Construção</v>
       </c>
       <c r="P37" s="70" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Q37" s="70" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R37" s="68" t="s">
         <v>1</v>
@@ -7478,7 +7509,7 @@
         <v>Etapa</v>
       </c>
       <c r="V37" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W37" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7503,16 +7534,16 @@
         <v>38</v>
       </c>
       <c r="B38" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D38" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F38" s="20" t="s">
         <v>71</v>
@@ -7549,10 +7580,10 @@
         <v>Operação</v>
       </c>
       <c r="P38" s="71" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q38" s="70" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R38" s="68" t="s">
         <v>1</v>
@@ -7570,7 +7601,7 @@
         <v>Etapa</v>
       </c>
       <c r="V38" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W38" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7595,19 +7626,19 @@
         <v>39</v>
       </c>
       <c r="B39" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C39" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C39" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D39" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G39" s="66" t="s">
         <v>1</v>
@@ -7641,10 +7672,10 @@
         <v>Inaugural</v>
       </c>
       <c r="P39" s="71" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q39" s="70" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R39" s="68" t="s">
         <v>1</v>
@@ -7662,7 +7693,7 @@
         <v>Histórico</v>
       </c>
       <c r="V39" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W39" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7687,19 +7718,19 @@
         <v>40</v>
       </c>
       <c r="B40" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C40" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C40" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D40" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G40" s="66" t="s">
         <v>1</v>
@@ -7733,10 +7764,10 @@
         <v>Modernizar</v>
       </c>
       <c r="P40" s="71" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q40" s="70" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R40" s="68" t="s">
         <v>1</v>
@@ -7754,7 +7785,7 @@
         <v>Histórico</v>
       </c>
       <c r="V40" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W40" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7779,19 +7810,19 @@
         <v>41</v>
       </c>
       <c r="B41" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C41" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C41" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G41" s="66" t="s">
         <v>1</v>
@@ -7825,10 +7856,10 @@
         <v>Troca</v>
       </c>
       <c r="P41" s="71" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q41" s="70" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R41" s="68" t="s">
         <v>1</v>
@@ -7846,7 +7877,7 @@
         <v>Histórico</v>
       </c>
       <c r="V41" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W41" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7871,16 +7902,16 @@
         <v>42</v>
       </c>
       <c r="B42" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C42" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C42" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E42" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F42" s="20" t="s">
         <v>109</v>
@@ -7917,10 +7948,10 @@
         <v>Operacional</v>
       </c>
       <c r="P42" s="71" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q42" s="70" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R42" s="68" t="s">
         <v>1</v>
@@ -7938,7 +7969,7 @@
         <v>Histórico</v>
       </c>
       <c r="V42" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W42" s="73" t="str">
         <f t="shared" si="8"/>
@@ -7963,19 +7994,19 @@
         <v>43</v>
       </c>
       <c r="B43" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="C43" s="29" t="s">
-        <v>253</v>
       </c>
       <c r="D43" s="29" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F43" s="53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G43" s="66" t="s">
         <v>1</v>
@@ -8009,10 +8040,10 @@
         <v>Reforma</v>
       </c>
       <c r="P43" s="71" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q43" s="70" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R43" s="68" t="s">
         <v>1</v>
@@ -8030,7 +8061,7 @@
         <v>Histórico</v>
       </c>
       <c r="V43" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W43" s="73" t="str">
         <f t="shared" si="8"/>
@@ -8055,19 +8086,19 @@
         <v>44</v>
       </c>
       <c r="B44" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>252</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>253</v>
       </c>
       <c r="D44" s="21" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F44" s="53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G44" s="66" t="s">
         <v>1</v>
@@ -8101,10 +8132,10 @@
         <v>Pericial</v>
       </c>
       <c r="P44" s="71" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Q44" s="71" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="R44" s="68" t="s">
         <v>1</v>
@@ -8122,7 +8153,7 @@
         <v>Histórico</v>
       </c>
       <c r="V44" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W44" s="73" t="str">
         <f t="shared" si="8"/>
@@ -8147,19 +8178,19 @@
         <v>45</v>
       </c>
       <c r="B45" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C45" s="21" t="s">
         <v>252</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>253</v>
       </c>
       <c r="D45" s="21" t="s">
         <v>59</v>
       </c>
       <c r="E45" s="21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F45" s="53" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G45" s="66" t="s">
         <v>1</v>
@@ -8193,10 +8224,10 @@
         <v>Congresso</v>
       </c>
       <c r="P45" s="71" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q45" s="71" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="R45" s="68" t="s">
         <v>1</v>
@@ -8214,7 +8245,7 @@
         <v>Agendado</v>
       </c>
       <c r="V45" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W45" s="73" t="str">
         <f t="shared" si="8"/>
@@ -8239,19 +8270,19 @@
         <v>46</v>
       </c>
       <c r="B46" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C46" s="21" t="s">
         <v>252</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>253</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>59</v>
       </c>
       <c r="E46" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="F46" s="53" t="s">
         <v>371</v>
-      </c>
-      <c r="F46" s="53" t="s">
-        <v>372</v>
       </c>
       <c r="G46" s="66" t="s">
         <v>1</v>
@@ -8285,10 +8316,10 @@
         <v>Reunião</v>
       </c>
       <c r="P46" s="71" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q46" s="71" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="R46" s="68" t="s">
         <v>1</v>
@@ -8306,7 +8337,7 @@
         <v>Agendado</v>
       </c>
       <c r="V46" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W46" s="73" t="str">
         <f t="shared" si="8"/>
@@ -8331,16 +8362,16 @@
         <v>47</v>
       </c>
       <c r="B47" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C47" s="21" t="s">
         <v>252</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>253</v>
       </c>
       <c r="D47" s="21" t="s">
         <v>59</v>
       </c>
       <c r="E47" s="21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F47" s="53" t="s">
         <v>107</v>
@@ -8377,10 +8408,10 @@
         <v>Entrega</v>
       </c>
       <c r="P47" s="71" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Q47" s="71" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R47" s="68" t="s">
         <v>1</v>
@@ -8398,7 +8429,7 @@
         <v>Agendado</v>
       </c>
       <c r="V47" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W47" s="73" t="str">
         <f t="shared" si="8"/>
@@ -8423,19 +8454,19 @@
         <v>48</v>
       </c>
       <c r="B48" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" s="21" t="s">
         <v>252</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>253</v>
       </c>
       <c r="D48" s="21" t="s">
         <v>59</v>
       </c>
       <c r="E48" s="21" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F48" s="53" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G48" s="66" t="s">
         <v>1</v>
@@ -8469,10 +8500,10 @@
         <v>Exame</v>
       </c>
       <c r="P48" s="71" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q48" s="71" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="R48" s="68" t="s">
         <v>1</v>
@@ -8490,7 +8521,7 @@
         <v>Agendado</v>
       </c>
       <c r="V48" s="56" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W48" s="73" t="str">
         <f t="shared" si="8"/>
@@ -8511,39 +8542,32 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA7:AA48 W2:W48">
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F42 F1">
-    <cfRule type="duplicateValues" dxfId="18" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F48 F1">
-    <cfRule type="duplicateValues" dxfId="17" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A48">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
+  <conditionalFormatting sqref="F7:F42 F1">
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F48 F1">
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:W48">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA48">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -8758,7 +8782,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8782,10 +8806,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="46" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="46" t="s">
         <v>255</v>
-      </c>
-      <c r="C1" s="46" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -8796,7 +8820,7 @@
         <v>54</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.4">
@@ -8804,15 +8828,15 @@
         <v>3</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A3">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8822,8 +8846,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5087910E-DA31-4318-A539-726BE963325D}">
-  <dimension ref="A1:W84"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Y84"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.3" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.4609375" bestFit="1" customWidth="1"/>
@@ -8839,20 +8863,22 @@
     <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3828125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.15234375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="39.765625" customWidth="1"/>
     <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.3046875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6.69140625" customWidth="1"/>
     <col min="19" max="19" width="3.53515625" customWidth="1"/>
     <col min="20" max="20" width="6.69140625" customWidth="1"/>
     <col min="21" max="21" width="4" customWidth="1"/>
-    <col min="22" max="22" width="6.69140625" style="62" customWidth="1"/>
-    <col min="23" max="23" width="4.69140625" style="62" customWidth="1"/>
+    <col min="22" max="22" width="2.3828125" style="62" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.84375" style="62" customWidth="1"/>
+    <col min="24" max="24" width="3.69140625" style="62" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.84375" style="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B1" s="35" t="s">
         <v>74</v>
@@ -8864,64 +8890,70 @@
         <v>48</v>
       </c>
       <c r="E1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="I1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="K1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="M1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N1" s="44" t="s">
         <v>48</v>
       </c>
       <c r="O1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="Q1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="S1" s="35" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="T1" s="49" t="s">
         <v>48</v>
       </c>
       <c r="U1" s="49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="V1" s="35" t="s">
         <v>48</v>
       </c>
       <c r="W1" s="35" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>191</v>
+      </c>
+      <c r="X1" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="34">
         <v>2</v>
       </c>
@@ -8965,7 +8997,7 @@
         <v>78</v>
       </c>
       <c r="O2" s="38" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="P2" s="33" t="s">
         <v>1</v>
@@ -8974,30 +9006,36 @@
         <v>1</v>
       </c>
       <c r="R2" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S2" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T2" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S2" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T2" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U2" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V2" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W2" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X2" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y2" s="38" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="34">
         <v>3</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C3" s="28" t="s">
         <v>51</v>
@@ -9036,7 +9074,7 @@
         <v>78</v>
       </c>
       <c r="O3" s="38" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P3" s="33" t="s">
         <v>1</v>
@@ -9045,30 +9083,36 @@
         <v>1</v>
       </c>
       <c r="R3" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S3" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T3" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S3" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T3" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U3" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V3" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W3" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X3" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y3" s="38" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="34">
         <v>4</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>51</v>
@@ -9107,7 +9151,7 @@
         <v>78</v>
       </c>
       <c r="O4" s="38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P4" s="33" t="s">
         <v>1</v>
@@ -9116,39 +9160,45 @@
         <v>1</v>
       </c>
       <c r="R4" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S4" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T4" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S4" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T4" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U4" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V4" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W4" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X4" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y4" s="38" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="34">
         <v>5</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>51</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F5" s="32" t="s">
         <v>1</v>
@@ -9178,7 +9228,7 @@
         <v>78</v>
       </c>
       <c r="O5" s="38" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P5" s="33" t="s">
         <v>1</v>
@@ -9187,45 +9237,51 @@
         <v>1</v>
       </c>
       <c r="R5" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S5" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T5" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S5" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T5" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U5" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V5" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W5" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X5" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y5" s="38" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="34">
         <v>6</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G6" s="54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H6" s="32" t="s">
         <v>1</v>
@@ -9249,7 +9305,7 @@
         <v>78</v>
       </c>
       <c r="O6" s="38" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P6" s="33" t="s">
         <v>1</v>
@@ -9258,45 +9314,51 @@
         <v>1</v>
       </c>
       <c r="R6" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S6" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T6" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S6" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T6" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U6" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V6" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W6" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X6" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y6" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="34">
         <v>7</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G7" s="54" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H7" s="32" t="s">
         <v>1</v>
@@ -9320,7 +9382,7 @@
         <v>78</v>
       </c>
       <c r="O7" s="38" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P7" s="33" t="s">
         <v>1</v>
@@ -9329,45 +9391,51 @@
         <v>1</v>
       </c>
       <c r="R7" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S7" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T7" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S7" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T7" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U7" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V7" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W7" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X7" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y7" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="34">
         <v>8</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G8" s="54" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H8" s="32" t="s">
         <v>1</v>
@@ -9391,7 +9459,7 @@
         <v>78</v>
       </c>
       <c r="O8" s="38" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P8" s="33" t="s">
         <v>1</v>
@@ -9400,45 +9468,51 @@
         <v>1</v>
       </c>
       <c r="R8" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S8" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T8" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S8" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T8" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U8" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V8" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W8" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X8" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y8" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="34">
         <v>9</v>
       </c>
       <c r="B9" s="52" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G9" s="54" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H9" s="32" t="s">
         <v>1</v>
@@ -9462,7 +9536,7 @@
         <v>78</v>
       </c>
       <c r="O9" s="38" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P9" s="33" t="s">
         <v>1</v>
@@ -9471,45 +9545,51 @@
         <v>1</v>
       </c>
       <c r="R9" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S9" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T9" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S9" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T9" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U9" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V9" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W9" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X9" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y9" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="34">
         <v>10</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H10" s="32" t="s">
         <v>1</v>
@@ -9533,7 +9613,7 @@
         <v>78</v>
       </c>
       <c r="O10" s="38" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P10" s="33" t="s">
         <v>1</v>
@@ -9542,45 +9622,51 @@
         <v>1</v>
       </c>
       <c r="R10" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S10" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T10" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S10" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T10" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U10" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V10" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W10" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X10" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y10" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="34">
         <v>11</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C11" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G11" s="54" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H11" s="32" t="s">
         <v>1</v>
@@ -9604,7 +9690,7 @@
         <v>78</v>
       </c>
       <c r="O11" s="38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P11" s="33" t="s">
         <v>1</v>
@@ -9613,45 +9699,51 @@
         <v>1</v>
       </c>
       <c r="R11" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S11" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T11" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S11" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T11" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U11" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V11" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W11" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X11" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y11" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="34">
         <v>12</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G12" s="54" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H12" s="32" t="s">
         <v>1</v>
@@ -9675,7 +9767,7 @@
         <v>78</v>
       </c>
       <c r="O12" s="38" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P12" s="33" t="s">
         <v>1</v>
@@ -9684,45 +9776,51 @@
         <v>1</v>
       </c>
       <c r="R12" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S12" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T12" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S12" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T12" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U12" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V12" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W12" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X12" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y12" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="34">
         <v>13</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H13" s="32" t="s">
         <v>1</v>
@@ -9746,7 +9844,7 @@
         <v>78</v>
       </c>
       <c r="O13" s="38" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="P13" s="33" t="s">
         <v>1</v>
@@ -9755,45 +9853,51 @@
         <v>1</v>
       </c>
       <c r="R13" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S13" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T13" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S13" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T13" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U13" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V13" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W13" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X13" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y13" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="34">
         <v>14</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H14" s="32" t="s">
         <v>1</v>
@@ -9817,7 +9921,7 @@
         <v>78</v>
       </c>
       <c r="O14" s="38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P14" s="33" t="s">
         <v>1</v>
@@ -9826,45 +9930,51 @@
         <v>1</v>
       </c>
       <c r="R14" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S14" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T14" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S14" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T14" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U14" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V14" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W14" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X14" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y14" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="34">
         <v>15</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C15" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G15" s="54" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>1</v>
@@ -9888,7 +9998,7 @@
         <v>78</v>
       </c>
       <c r="O15" s="38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P15" s="33" t="s">
         <v>1</v>
@@ -9897,45 +10007,51 @@
         <v>1</v>
       </c>
       <c r="R15" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S15" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T15" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S15" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T15" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U15" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V15" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W15" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X15" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y15" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="34">
         <v>16</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C16" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G16" s="54" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H16" s="32" t="s">
         <v>1</v>
@@ -9959,7 +10075,7 @@
         <v>78</v>
       </c>
       <c r="O16" s="38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P16" s="33" t="s">
         <v>1</v>
@@ -9968,39 +10084,45 @@
         <v>1</v>
       </c>
       <c r="R16" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S16" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T16" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S16" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T16" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U16" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V16" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W16" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X16" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y16" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="34">
         <v>17</v>
       </c>
       <c r="B17" s="52" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C17" s="28" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F17" s="32" t="s">
         <v>1</v>
@@ -10030,7 +10152,7 @@
         <v>78</v>
       </c>
       <c r="O17" s="38" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P17" s="33" t="s">
         <v>1</v>
@@ -10039,45 +10161,51 @@
         <v>1</v>
       </c>
       <c r="R17" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S17" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T17" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S17" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T17" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U17" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V17" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W17" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X17" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y17" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="34">
         <v>18</v>
       </c>
       <c r="B18" s="52" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E18" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G18" s="37" t="s">
         <v>324</v>
-      </c>
-      <c r="F18" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>325</v>
       </c>
       <c r="H18" s="32" t="s">
         <v>1</v>
@@ -10101,7 +10229,7 @@
         <v>78</v>
       </c>
       <c r="O18" s="38" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P18" s="33" t="s">
         <v>1</v>
@@ -10110,45 +10238,51 @@
         <v>1</v>
       </c>
       <c r="R18" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S18" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T18" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S18" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T18" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U18" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V18" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W18" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X18" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y18" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="34">
         <v>19</v>
       </c>
       <c r="B19" s="52" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E19" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G19" s="37" t="s">
         <v>326</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>327</v>
       </c>
       <c r="H19" s="32" t="s">
         <v>1</v>
@@ -10172,7 +10306,7 @@
         <v>78</v>
       </c>
       <c r="O19" s="38" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P19" s="33" t="s">
         <v>1</v>
@@ -10181,57 +10315,63 @@
         <v>1</v>
       </c>
       <c r="R19" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S19" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T19" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S19" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T19" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U19" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V19" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W19" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X19" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y19" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="34">
         <v>20</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E20" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G20" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="F20" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G20" s="37" t="s">
+      <c r="H20" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="I20" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="H20" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I20" s="37" t="s">
+      <c r="J20" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="K20" s="37" t="s">
         <v>277</v>
-      </c>
-      <c r="J20" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="K20" s="37" t="s">
-        <v>278</v>
       </c>
       <c r="L20" s="32" t="s">
         <v>1</v>
@@ -10243,7 +10383,7 @@
         <v>78</v>
       </c>
       <c r="O20" s="38" t="s">
-        <v>386</v>
+        <v>469</v>
       </c>
       <c r="P20" s="33" t="s">
         <v>1</v>
@@ -10252,57 +10392,63 @@
         <v>1</v>
       </c>
       <c r="R20" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S20" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T20" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S20" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T20" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U20" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V20" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W20" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X20" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y20" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="34">
         <v>21</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E21" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G21" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="F21" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G21" s="37" t="s">
+      <c r="H21" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="I21" s="37" t="s">
         <v>280</v>
       </c>
-      <c r="H21" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I21" s="37" t="s">
+      <c r="J21" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="K21" s="37" t="s">
         <v>281</v>
-      </c>
-      <c r="J21" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="K21" s="37" t="s">
-        <v>282</v>
       </c>
       <c r="L21" s="32" t="s">
         <v>1</v>
@@ -10314,7 +10460,7 @@
         <v>78</v>
       </c>
       <c r="O21" s="38" t="s">
-        <v>387</v>
+        <v>470</v>
       </c>
       <c r="P21" s="33" t="s">
         <v>1</v>
@@ -10323,57 +10469,63 @@
         <v>1</v>
       </c>
       <c r="R21" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S21" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T21" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S21" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T21" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U21" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V21" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W21" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X21" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y21" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="34">
         <v>22</v>
       </c>
       <c r="B22" s="52" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E22" s="37" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G22" s="37" t="s">
         <v>283</v>
       </c>
-      <c r="F22" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G22" s="37" t="s">
+      <c r="H22" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="I22" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="H22" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I22" s="37" t="s">
+      <c r="J22" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="K22" s="37" t="s">
         <v>285</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="K22" s="37" t="s">
-        <v>286</v>
       </c>
       <c r="L22" s="32" t="s">
         <v>1</v>
@@ -10385,7 +10537,7 @@
         <v>78</v>
       </c>
       <c r="O22" s="38" t="s">
-        <v>388</v>
+        <v>471</v>
       </c>
       <c r="P22" s="33" t="s">
         <v>1</v>
@@ -10394,51 +10546,57 @@
         <v>1</v>
       </c>
       <c r="R22" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S22" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T22" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S22" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T22" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U22" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V22" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W22" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X22" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y22" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="34">
         <v>23</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E23" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G23" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="F23" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G23" s="37" t="s">
+      <c r="H23" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="I23" s="37" t="s">
         <v>276</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>277</v>
       </c>
       <c r="J23" s="32" t="s">
         <v>1</v>
@@ -10456,7 +10614,7 @@
         <v>78</v>
       </c>
       <c r="O23" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P23" s="33" t="s">
         <v>1</v>
@@ -10465,51 +10623,57 @@
         <v>1</v>
       </c>
       <c r="R23" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S23" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T23" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S23" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T23" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U23" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V23" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W23" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X23" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y23" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="34">
         <v>24</v>
       </c>
       <c r="B24" s="52" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E24" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G24" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="F24" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G24" s="37" t="s">
+      <c r="H24" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="I24" s="37" t="s">
         <v>279</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>280</v>
       </c>
       <c r="J24" s="32" t="s">
         <v>1</v>
@@ -10527,7 +10691,7 @@
         <v>78</v>
       </c>
       <c r="O24" s="38" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P24" s="33" t="s">
         <v>1</v>
@@ -10536,51 +10700,57 @@
         <v>1</v>
       </c>
       <c r="R24" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S24" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T24" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S24" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T24" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U24" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V24" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W24" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X24" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y24" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="34">
         <v>25</v>
       </c>
       <c r="B25" s="52" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E25" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G25" s="37" t="s">
         <v>281</v>
       </c>
-      <c r="F25" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G25" s="37" t="s">
+      <c r="H25" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="I25" s="37" t="s">
         <v>282</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>283</v>
       </c>
       <c r="J25" s="32" t="s">
         <v>1</v>
@@ -10598,7 +10768,7 @@
         <v>78</v>
       </c>
       <c r="O25" s="38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P25" s="33" t="s">
         <v>1</v>
@@ -10607,51 +10777,57 @@
         <v>1</v>
       </c>
       <c r="R25" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S25" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T25" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S25" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T25" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U25" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V25" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W25" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X25" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y25" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="34">
         <v>26</v>
       </c>
       <c r="B26" s="52" t="s">
+        <v>326</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>327</v>
       </c>
-      <c r="C26" s="28" t="s">
-        <v>328</v>
-      </c>
       <c r="D26" s="32" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E26" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="G26" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="F26" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="G26" s="37" t="s">
+      <c r="H26" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="I26" s="37" t="s">
         <v>285</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="I26" s="37" t="s">
-        <v>286</v>
       </c>
       <c r="J26" s="32" t="s">
         <v>1</v>
@@ -10669,7 +10845,7 @@
         <v>78</v>
       </c>
       <c r="O26" s="38" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P26" s="33" t="s">
         <v>1</v>
@@ -10678,30 +10854,36 @@
         <v>1</v>
       </c>
       <c r="R26" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S26" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T26" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S26" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T26" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U26" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V26" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W26" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X26" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y26" s="38" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="34">
         <v>27</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C27" s="28" t="s">
         <v>54</v>
@@ -10740,7 +10922,7 @@
         <v>78</v>
       </c>
       <c r="O27" s="38" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P27" s="33" t="s">
         <v>1</v>
@@ -10749,30 +10931,36 @@
         <v>1</v>
       </c>
       <c r="R27" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S27" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T27" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S27" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T27" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U27" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V27" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W27" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X27" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y27" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="34">
         <v>28</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>54</v>
@@ -10811,7 +10999,7 @@
         <v>78</v>
       </c>
       <c r="O28" s="38" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P28" s="33" t="s">
         <v>1</v>
@@ -10820,30 +11008,36 @@
         <v>1</v>
       </c>
       <c r="R28" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S28" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T28" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S28" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T28" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U28" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V28" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W28" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X28" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y28" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="34">
         <v>29</v>
       </c>
       <c r="B29" s="52" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>54</v>
@@ -10882,7 +11076,7 @@
         <v>78</v>
       </c>
       <c r="O29" s="38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P29" s="33" t="s">
         <v>1</v>
@@ -10891,30 +11085,36 @@
         <v>1</v>
       </c>
       <c r="R29" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S29" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T29" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S29" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T29" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U29" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V29" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W29" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X29" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y29" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="34">
         <v>30</v>
       </c>
       <c r="B30" s="52" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>54</v>
@@ -10953,7 +11153,7 @@
         <v>78</v>
       </c>
       <c r="O30" s="38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P30" s="33" t="s">
         <v>1</v>
@@ -10962,30 +11162,36 @@
         <v>1</v>
       </c>
       <c r="R30" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S30" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T30" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S30" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T30" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U30" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V30" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W30" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X30" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y30" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="34">
         <v>31</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>54</v>
@@ -11024,7 +11230,7 @@
         <v>78</v>
       </c>
       <c r="O31" s="38" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P31" s="33" t="s">
         <v>1</v>
@@ -11033,30 +11239,36 @@
         <v>1</v>
       </c>
       <c r="R31" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S31" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T31" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S31" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T31" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U31" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V31" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W31" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X31" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y31" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="34">
         <v>32</v>
       </c>
       <c r="B32" s="52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C32" s="28" t="s">
         <v>54</v>
@@ -11095,7 +11307,7 @@
         <v>78</v>
       </c>
       <c r="O32" s="38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P32" s="33" t="s">
         <v>1</v>
@@ -11104,30 +11316,36 @@
         <v>1</v>
       </c>
       <c r="R32" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S32" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T32" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S32" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T32" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U32" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V32" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W32" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X32" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y32" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="34">
         <v>33</v>
       </c>
       <c r="B33" s="52" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C33" s="28" t="s">
         <v>54</v>
@@ -11166,7 +11384,7 @@
         <v>78</v>
       </c>
       <c r="O33" s="38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P33" s="33" t="s">
         <v>1</v>
@@ -11175,45 +11393,51 @@
         <v>1</v>
       </c>
       <c r="R33" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S33" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T33" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S33" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T33" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U33" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V33" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W33" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X33" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y33" s="38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="34">
         <v>34</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C34" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D34" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E34" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="E34" s="54" t="s">
+      <c r="F34" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="G34" s="37" t="s">
         <v>274</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>275</v>
       </c>
       <c r="H34" s="32" t="s">
         <v>1</v>
@@ -11237,7 +11461,7 @@
         <v>78</v>
       </c>
       <c r="O34" s="38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P34" s="33" t="s">
         <v>1</v>
@@ -11246,45 +11470,52 @@
         <v>1</v>
       </c>
       <c r="R34" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S34" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T34" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S34" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T34" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U34" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V34" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W34" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X34" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y34" s="38" t="str">
+        <f t="shared" ref="Y3:Y66" si="0">B34</f>
+        <v>Jan.2025</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="34">
         <v>35</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C35" s="21" t="s">
         <v>61</v>
       </c>
       <c r="D35" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E35" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="E35" s="54" t="s">
+      <c r="F35" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="F35" s="32" t="s">
-        <v>274</v>
-      </c>
       <c r="G35" s="37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H35" s="32" t="s">
         <v>1</v>
@@ -11308,7 +11539,7 @@
         <v>78</v>
       </c>
       <c r="O35" s="38" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P35" s="33" t="s">
         <v>1</v>
@@ -11317,30 +11548,37 @@
         <v>1</v>
       </c>
       <c r="R35" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S35" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T35" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S35" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T35" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U35" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V35" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W35" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X35" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y35" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Dez.2025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="34">
         <v>36</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C36" s="21" t="s">
         <v>61</v>
@@ -11382,36 +11620,43 @@
         <v>87</v>
       </c>
       <c r="P36" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q36" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R36" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S36" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T36" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S36" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T36" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U36" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V36" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W36" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X36" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y36" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Data.I01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="34">
         <v>37</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>61</v>
@@ -11453,36 +11698,43 @@
         <v>84</v>
       </c>
       <c r="P37" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q37" s="38" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R37" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S37" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T37" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S37" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T37" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U37" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V37" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W37" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X37" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y37" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Data.F01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="34">
         <v>38</v>
       </c>
       <c r="B38" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C38" s="21" t="s">
         <v>72</v>
@@ -11521,39 +11773,45 @@
         <v>78</v>
       </c>
       <c r="O38" s="38" t="s">
-        <v>124</v>
+        <v>472</v>
       </c>
       <c r="P38" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q38" s="38" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R38" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S38" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T38" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S38" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T38" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U38" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V38" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W38" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X38" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y38" s="38" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="34">
         <v>39</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C39" s="21" t="s">
         <v>72</v>
@@ -11592,42 +11850,48 @@
         <v>78</v>
       </c>
       <c r="O39" s="38" t="s">
-        <v>124</v>
+        <v>472</v>
       </c>
       <c r="P39" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q39" s="38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R39" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S39" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T39" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S39" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T39" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U39" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V39" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W39" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X39" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y39" s="38" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="34">
         <v>40</v>
       </c>
       <c r="B40" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D40" s="32" t="s">
         <v>1</v>
@@ -11666,39 +11930,45 @@
         <v>93</v>
       </c>
       <c r="P40" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q40" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R40" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S40" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T40" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S40" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T40" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U40" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V40" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W40" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X40" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y40" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="34">
         <v>41</v>
       </c>
       <c r="B41" s="41" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D41" s="32" t="s">
         <v>1</v>
@@ -11737,39 +12007,45 @@
         <v>95</v>
       </c>
       <c r="P41" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q41" s="38" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R41" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S41" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T41" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S41" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T41" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U41" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V41" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W41" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X41" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y41" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="34">
         <v>42</v>
       </c>
       <c r="B42" s="41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D42" s="32" t="s">
         <v>1</v>
@@ -11808,39 +12084,45 @@
         <v>92</v>
       </c>
       <c r="P42" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q42" s="38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R42" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S42" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T42" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S42" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T42" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U42" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V42" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W42" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X42" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y42" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="34">
         <v>43</v>
       </c>
       <c r="B43" s="41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D43" s="32" t="s">
         <v>1</v>
@@ -11879,31 +12161,37 @@
         <v>94</v>
       </c>
       <c r="P43" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q43" s="38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="R43" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S43" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T43" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S43" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T43" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U43" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V43" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W43" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X43" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y43" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="34">
         <v>44</v>
       </c>
@@ -11950,31 +12238,37 @@
         <v>79</v>
       </c>
       <c r="P44" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q44" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R44" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S44" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T44" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S44" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T44" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U44" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V44" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W44" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X44" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y44" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="34">
         <v>45</v>
       </c>
@@ -12021,31 +12315,37 @@
         <v>81</v>
       </c>
       <c r="P45" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q45" s="38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R45" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S45" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T45" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S45" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T45" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U45" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V45" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W45" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X45" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y45" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="34">
         <v>46</v>
       </c>
@@ -12053,7 +12353,7 @@
         <v>77</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D46" s="32" t="s">
         <v>1</v>
@@ -12092,31 +12392,37 @@
         <v>96</v>
       </c>
       <c r="P46" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q46" s="38" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R46" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S46" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T46" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S46" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T46" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U46" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V46" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W46" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X46" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y46" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="34">
         <v>47</v>
       </c>
@@ -12124,7 +12430,7 @@
         <v>97</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D47" s="32" t="s">
         <v>1</v>
@@ -12163,31 +12469,37 @@
         <v>98</v>
       </c>
       <c r="P47" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q47" s="38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R47" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S47" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T47" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S47" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T47" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U47" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V47" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W47" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X47" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y47" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="34">
         <v>48</v>
       </c>
@@ -12195,10 +12507,10 @@
         <v>99</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E48" s="37" t="s">
         <v>97</v>
@@ -12234,31 +12546,37 @@
         <v>100</v>
       </c>
       <c r="P48" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q48" s="38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R48" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S48" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T48" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S48" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T48" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U48" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V48" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W48" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X48" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y48" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="34">
         <v>49</v>
       </c>
@@ -12266,10 +12584,10 @@
         <v>101</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E49" s="37" t="s">
         <v>97</v>
@@ -12305,31 +12623,37 @@
         <v>102</v>
       </c>
       <c r="P49" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q49" s="38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="R49" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S49" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T49" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S49" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T49" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U49" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V49" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W49" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X49" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y49" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="34">
         <v>50</v>
       </c>
@@ -12337,10 +12661,10 @@
         <v>103</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E50" s="37" t="s">
         <v>97</v>
@@ -12376,31 +12700,37 @@
         <v>104</v>
       </c>
       <c r="P50" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q50" s="38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R50" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S50" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T50" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S50" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T50" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U50" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V50" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W50" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X50" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y50" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="34">
         <v>51</v>
       </c>
@@ -12408,10 +12738,10 @@
         <v>105</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>101</v>
@@ -12447,31 +12777,37 @@
         <v>106</v>
       </c>
       <c r="P51" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R51" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S51" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T51" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S51" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T51" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U51" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V51" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W51" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X51" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y51" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="34">
         <v>52</v>
       </c>
@@ -12479,10 +12815,10 @@
         <v>107</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E52" s="37" t="s">
         <v>105</v>
@@ -12518,31 +12854,37 @@
         <v>108</v>
       </c>
       <c r="P52" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="38" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R52" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S52" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T52" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S52" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T52" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U52" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V52" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W52" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X52" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y52" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="34">
         <v>53</v>
       </c>
@@ -12550,10 +12892,10 @@
         <v>109</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E53" s="37" t="s">
         <v>105</v>
@@ -12589,36 +12931,43 @@
         <v>110</v>
       </c>
       <c r="P53" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="38" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R53" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S53" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T53" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S53" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T53" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U53" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V53" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W53" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X53" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y53" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Operacional</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="34">
         <v>54</v>
       </c>
       <c r="B54" s="41" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C54" s="21" t="s">
         <v>59</v>
@@ -12657,39 +13006,46 @@
         <v>78</v>
       </c>
       <c r="O54" s="38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P54" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R54" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S54" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T54" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S54" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T54" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U54" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V54" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W54" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X54" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y54" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Obrigatório</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="34">
         <v>55</v>
       </c>
       <c r="B55" s="41" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C55" s="21" t="s">
         <v>59</v>
@@ -12728,39 +13084,46 @@
         <v>78</v>
       </c>
       <c r="O55" s="38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P55" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="R55" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S55" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T55" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S55" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T55" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U55" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V55" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W55" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X55" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y55" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Opcional</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="34">
         <v>56</v>
       </c>
       <c r="B56" s="41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C56" s="21" t="s">
         <v>59</v>
@@ -12799,39 +13162,46 @@
         <v>78</v>
       </c>
       <c r="O56" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P56" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R56" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S56" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T56" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S56" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T56" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U56" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V56" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W56" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X56" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y56" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Esperado</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="34">
         <v>57</v>
       </c>
       <c r="B57" s="41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" s="21" t="s">
         <v>59</v>
@@ -12870,39 +13240,46 @@
         <v>78</v>
       </c>
       <c r="O57" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P57" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="R57" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S57" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T57" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S57" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T57" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U57" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V57" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W57" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X57" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y57" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Inesperado</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="34">
         <v>58</v>
       </c>
       <c r="B58" s="41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C58" s="21" t="s">
         <v>59</v>
@@ -12941,39 +13318,46 @@
         <v>78</v>
       </c>
       <c r="O58" s="38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P58" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R58" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S58" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T58" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S58" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T58" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U58" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V58" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W58" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X58" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y58" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Único</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="34">
         <v>59</v>
       </c>
       <c r="B59" s="41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C59" s="21" t="s">
         <v>59</v>
@@ -13012,39 +13396,46 @@
         <v>78</v>
       </c>
       <c r="O59" s="38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P59" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q59" s="38" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R59" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S59" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T59" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S59" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T59" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U59" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V59" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W59" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X59" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y59" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Regular</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="34">
         <v>60</v>
       </c>
       <c r="B60" s="41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C60" s="21" t="s">
         <v>59</v>
@@ -13083,39 +13474,46 @@
         <v>78</v>
       </c>
       <c r="O60" s="38" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P60" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q60" s="38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R60" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S60" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T60" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S60" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T60" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U60" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V60" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W60" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X60" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y60" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Periódico</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="34">
         <v>61</v>
       </c>
       <c r="B61" s="41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C61" s="21" t="s">
         <v>59</v>
@@ -13154,34 +13552,41 @@
         <v>78</v>
       </c>
       <c r="O61" s="38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P61" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q61" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R61" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S61" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T61" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S61" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T61" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U61" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V61" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W61" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X61" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y61" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Aperiódico</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="34">
         <v>62</v>
       </c>
@@ -13228,31 +13633,37 @@
         <v>83</v>
       </c>
       <c r="P62" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q62" s="38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R62" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S62" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T62" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S62" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T62" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U62" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V62" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W62" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X62" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y62" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="34">
         <v>63</v>
       </c>
@@ -13299,31 +13710,37 @@
         <v>86</v>
       </c>
       <c r="P63" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q63" s="38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R63" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S63" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T63" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S63" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T63" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U63" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V63" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W63" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X63" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y63" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="34">
         <v>64</v>
       </c>
@@ -13370,31 +13787,37 @@
         <v>89</v>
       </c>
       <c r="P64" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q64" s="38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="R64" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S64" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T64" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S64" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T64" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U64" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V64" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W64" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X64" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y64" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="34">
         <v>65</v>
       </c>
@@ -13441,31 +13864,37 @@
         <v>91</v>
       </c>
       <c r="P65" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q65" s="38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R65" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S65" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T65" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S65" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T65" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U65" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V65" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W65" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X65" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y65" s="38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="34">
         <v>66</v>
       </c>
@@ -13512,31 +13941,38 @@
         <v>112</v>
       </c>
       <c r="P66" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q66" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R66" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S66" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T66" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S66" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T66" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U66" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V66" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W66" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X66" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y66" s="38" t="str">
+        <f t="shared" si="0"/>
+        <v>Reunião.Investidores</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="34">
         <v>67</v>
       </c>
@@ -13583,31 +14019,37 @@
         <v>114</v>
       </c>
       <c r="P67" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q67" s="38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R67" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S67" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T67" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S67" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T67" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U67" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V67" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W67" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X67" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y67" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="34">
         <v>68</v>
       </c>
@@ -13654,31 +14096,37 @@
         <v>114</v>
       </c>
       <c r="P68" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q68" s="38" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R68" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S68" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T68" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S68" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T68" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U68" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V68" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W68" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X68" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y68" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="34">
         <v>69</v>
       </c>
@@ -13725,36 +14173,42 @@
         <v>114</v>
       </c>
       <c r="P69" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q69" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R69" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S69" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T69" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S69" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T69" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U69" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V69" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W69" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X69" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y69" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="34">
         <v>70</v>
       </c>
       <c r="B70" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C70" s="21" t="s">
         <v>71</v>
@@ -13793,39 +14247,45 @@
         <v>78</v>
       </c>
       <c r="O70" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P70" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q70" s="38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R70" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S70" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T70" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S70" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T70" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U70" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V70" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W70" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X70" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y70" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="34">
         <v>71</v>
       </c>
       <c r="B71" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C71" s="21" t="s">
         <v>71</v>
@@ -13864,34 +14324,40 @@
         <v>78</v>
       </c>
       <c r="O71" s="38" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P71" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q71" s="38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R71" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S71" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T71" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S71" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T71" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U71" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V71" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W71" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X71" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y71" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="34">
         <v>72</v>
       </c>
@@ -13938,31 +14404,37 @@
         <v>122</v>
       </c>
       <c r="P72" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="R72" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S72" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T72" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S72" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T72" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U72" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V72" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W72" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X72" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y72" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="34">
         <v>73</v>
       </c>
@@ -14009,31 +14481,37 @@
         <v>122</v>
       </c>
       <c r="P73" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q73" s="38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R73" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S73" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T73" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S73" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T73" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U73" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V73" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W73" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X73" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y73" s="38" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="34">
         <v>74</v>
       </c>
@@ -14080,31 +14558,37 @@
         <v>114</v>
       </c>
       <c r="P74" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q74" s="38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R74" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S74" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T74" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S74" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T74" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U74" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V74" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W74" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X74" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y74" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="34">
         <v>75</v>
       </c>
@@ -14115,7 +14599,7 @@
         <v>73</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E75" s="37" t="s">
         <v>117</v>
@@ -14151,42 +14635,48 @@
         <v>114</v>
       </c>
       <c r="P75" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q75" s="38" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R75" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S75" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T75" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S75" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T75" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U75" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V75" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W75" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X75" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y75" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="34">
         <v>76</v>
       </c>
       <c r="B76" s="42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C76" s="21" t="s">
         <v>73</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E76" s="37" t="s">
         <v>117</v>
@@ -14222,31 +14712,37 @@
         <v>114</v>
       </c>
       <c r="P76" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q76" s="38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R76" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S76" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T76" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S76" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T76" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U76" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V76" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W76" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X76" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y76" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="34">
         <v>77</v>
       </c>
@@ -14257,7 +14753,7 @@
         <v>73</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E77" s="37" t="s">
         <v>117</v>
@@ -14293,45 +14789,51 @@
         <v>114</v>
       </c>
       <c r="P77" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q77" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R77" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S77" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T77" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S77" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T77" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U77" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V77" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W77" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X77" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y77" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="34">
         <v>78</v>
       </c>
       <c r="B78" s="41" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C78" s="21" t="s">
         <v>73</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E78" s="37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F78" s="32" t="s">
         <v>1</v>
@@ -14364,45 +14866,51 @@
         <v>114</v>
       </c>
       <c r="P78" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q78" s="38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R78" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S78" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T78" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S78" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T78" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U78" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V78" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W78" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X78" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y78" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="34">
         <v>79</v>
       </c>
       <c r="B79" s="41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C79" s="21" t="s">
         <v>73</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E79" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F79" s="32" t="s">
         <v>1</v>
@@ -14435,31 +14943,37 @@
         <v>114</v>
       </c>
       <c r="P79" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q79" s="38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="R79" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S79" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T79" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S79" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T79" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U79" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V79" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W79" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X79" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y79" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="34">
         <v>80</v>
       </c>
@@ -14470,10 +14984,10 @@
         <v>69</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E80" s="37" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F80" s="32" t="s">
         <v>1</v>
@@ -14503,48 +15017,54 @@
         <v>78</v>
       </c>
       <c r="O80" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P80" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q80" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R80" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S80" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T80" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S80" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T80" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U80" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V80" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W80" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X80" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y80" s="38" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="34">
         <v>81</v>
       </c>
       <c r="B81" s="41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C81" s="21" t="s">
         <v>69</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E81" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F81" s="32" t="s">
         <v>1</v>
@@ -14574,48 +15094,54 @@
         <v>78</v>
       </c>
       <c r="O81" s="38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P81" s="33" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q81" s="38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="R81" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S81" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T81" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S81" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T81" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U81" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V81" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W81" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X81" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y81" s="38" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="34">
         <v>82</v>
       </c>
       <c r="B82" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D82" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E82" s="37" t="s">
         <v>272</v>
-      </c>
-      <c r="E82" s="37" t="s">
-        <v>273</v>
       </c>
       <c r="F82" s="32" t="s">
         <v>1</v>
@@ -14645,7 +15171,7 @@
         <v>78</v>
       </c>
       <c r="O82" s="38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P82" s="33" t="s">
         <v>1</v>
@@ -14654,39 +15180,45 @@
         <v>1</v>
       </c>
       <c r="R82" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S82" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T82" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S82" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T82" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U82" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V82" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W82" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X82" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y82" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="34">
         <v>83</v>
       </c>
       <c r="B83" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="C83" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="C83" s="53" t="s">
-        <v>270</v>
-      </c>
-      <c r="D83" s="32" t="s">
+      <c r="E83" s="37" t="s">
         <v>272</v>
-      </c>
-      <c r="E83" s="37" t="s">
-        <v>273</v>
       </c>
       <c r="F83" s="32" t="s">
         <v>1</v>
@@ -14716,7 +15248,7 @@
         <v>78</v>
       </c>
       <c r="O83" s="38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="P83" s="33" t="s">
         <v>1</v>
@@ -14725,39 +15257,45 @@
         <v>1</v>
       </c>
       <c r="R83" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S83" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T83" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S83" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T83" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U83" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V83" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W83" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>474</v>
+      </c>
+      <c r="X83" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y83" s="38" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="34">
         <v>84</v>
       </c>
       <c r="B84" s="52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C84" s="53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D84" s="32" t="s">
+        <v>271</v>
+      </c>
+      <c r="E84" s="37" t="s">
         <v>272</v>
-      </c>
-      <c r="E84" s="37" t="s">
-        <v>273</v>
       </c>
       <c r="F84" s="32" t="s">
         <v>1</v>
@@ -14787,7 +15325,7 @@
         <v>78</v>
       </c>
       <c r="O84" s="38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P84" s="33" t="s">
         <v>1</v>
@@ -14796,45 +15334,51 @@
         <v>1</v>
       </c>
       <c r="R84" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="S84" s="38" t="s">
+        <v>483</v>
+      </c>
+      <c r="T84" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="S84" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="T84" s="33" t="s">
-        <v>449</v>
-      </c>
       <c r="U84" s="38" t="s">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="V84" s="33" t="s">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="W84" s="38" t="s">
-        <v>1</v>
+        <v>474</v>
+      </c>
+      <c r="X84" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="Y84" s="38" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1 B38:B81 B34:B35">
-    <cfRule type="duplicateValues" dxfId="8" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B82">
-    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G16">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/CRON/Ontologia_CRONO.xlsx
+++ b/Versão5/CRON/Ontologia_CRONO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CRON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100D8441-2E28-463F-8561-B598E1C331CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B770377-947B-49C4-99EC-0E4AEE39CF2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2997" uniqueCount="484">
   <si>
     <t>Key</t>
   </si>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46143.59318935185</v>
+        <v>46143.682646064815</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>440</v>
@@ -11490,9 +11490,8 @@
       <c r="X34" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y34" s="38" t="str">
-        <f t="shared" ref="Y3:Y66" si="0">B34</f>
-        <v>Jan.2025</v>
+      <c r="Y34" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -11568,9 +11567,8 @@
       <c r="X35" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y35" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Dez.2025</v>
+      <c r="Y35" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -11646,9 +11644,8 @@
       <c r="X36" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y36" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Data.I01</v>
+      <c r="Y36" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -11724,9 +11721,8 @@
       <c r="X37" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y37" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Data.F01</v>
+      <c r="Y37" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -12957,9 +12953,8 @@
       <c r="X53" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y53" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Operacional</v>
+      <c r="Y53" s="38" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="54" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13035,9 +13030,8 @@
       <c r="X54" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y54" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Obrigatório</v>
+      <c r="Y54" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="55" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13113,9 +13107,8 @@
       <c r="X55" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y55" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Opcional</v>
+      <c r="Y55" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="56" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13191,9 +13184,8 @@
       <c r="X56" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y56" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Esperado</v>
+      <c r="Y56" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="57" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13269,9 +13261,8 @@
       <c r="X57" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y57" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Inesperado</v>
+      <c r="Y57" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="58" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13347,9 +13338,8 @@
       <c r="X58" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y58" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Único</v>
+      <c r="Y58" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13425,9 +13415,8 @@
       <c r="X59" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y59" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Regular</v>
+      <c r="Y59" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="60" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13503,9 +13492,8 @@
       <c r="X60" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y60" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Periódico</v>
+      <c r="Y60" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="61" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13581,9 +13569,8 @@
       <c r="X61" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y61" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Aperiódico</v>
+      <c r="Y61" s="38" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="62" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -13967,9 +13954,8 @@
       <c r="X66" s="33" t="s">
         <v>475</v>
       </c>
-      <c r="Y66" s="38" t="str">
-        <f t="shared" si="0"/>
-        <v>Reunião.Investidores</v>
+      <c r="Y66" s="38" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="67" spans="1:25" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">

--- a/Versão5/CRON/Ontologia_CRONO.xlsx
+++ b/Versão5/CRON/Ontologia_CRONO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\CRON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8319E273-4CC0-4B3C-A7FB-75FD960D5DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8B365E-9C3C-4957-A08B-780CD85F8F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -3447,7 +3447,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4178,7 +4198,7 @@
       </c>
       <c r="B18" s="17">
         <f ca="1">NOW()</f>
-        <v>46143.711679282409</v>
+        <v>46214.368819097224</v>
       </c>
       <c r="C18" s="58" t="s">
         <v>372</v>
@@ -8762,29 +8782,29 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A49">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F7:F43">
-    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1 F7:F49">
-    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W49">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA49">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9001,7 +9021,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9066,7 +9086,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9079,31 +9099,31 @@
   <dimension ref="A1:Y84"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="7.3" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.4609375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.23046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.53515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.3046875" customWidth="1"/>
+    <col min="7" max="7" width="2.23046875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.3828125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="39.765625" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.15234375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.61328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.3046875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.69140625" customWidth="1"/>
-    <col min="19" max="19" width="3.53515625" customWidth="1"/>
-    <col min="20" max="20" width="6.69140625" customWidth="1"/>
-    <col min="21" max="21" width="4" customWidth="1"/>
+    <col min="18" max="18" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="1.921875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="2.3828125" style="62" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.84375" style="62" customWidth="1"/>
-    <col min="24" max="24" width="3.69140625" style="62" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.84375" style="62" customWidth="1"/>
+    <col min="23" max="23" width="6.3046875" style="62" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.61328125" style="62" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.84375" style="62" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
@@ -15579,34 +15599,36 @@
     <sortCondition ref="C63:C78"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B1 B34:B35 B38:B78">
+    <cfRule type="duplicateValues" dxfId="12" priority="37"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B76">
-    <cfRule type="duplicateValues" dxfId="9" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B79">
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B80:B81">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:B84">
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C42">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C43">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G6:G7">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B80:B81">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B82:B84">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1 B34:B35 B38:B78">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
